--- a/data/trans_bre/P16A01-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A01-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 5,04</t>
+          <t>-4,18; 4,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 5,03</t>
+          <t>-6,26; 5,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 2,84</t>
+          <t>-7,41; 2,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 2,69</t>
+          <t>-5,95; 2,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,74; 104,35</t>
+          <t>-48,35; 103,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-41,88; 51,39</t>
+          <t>-42,24; 51,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-50,67; 35,32</t>
+          <t>-53,4; 34,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-54,89; 49,92</t>
+          <t>-53,04; 45,14</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 2,69</t>
+          <t>-3,88; 2,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,77; -0,3</t>
+          <t>-8,42; -0,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 3,32</t>
+          <t>-3,2; 3,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 6,16</t>
+          <t>-0,2; 5,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,63; 55,4</t>
+          <t>-45,95; 57,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,61; -0,42</t>
+          <t>-54,7; -5,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,61; 56,35</t>
+          <t>-35,25; 61,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 254,09</t>
+          <t>-7,43; 262,09</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 0,39</t>
+          <t>-5,39; 0,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 5,03</t>
+          <t>-5,43; 4,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 5,86</t>
+          <t>-2,3; 6,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 6,24</t>
+          <t>-1,14; 6,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-84,16; 22,45</t>
+          <t>-83,21; 17,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-36,16; 60,76</t>
+          <t>-41,78; 51,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-30,83; 134,08</t>
+          <t>-32,48; 142,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 132,29</t>
+          <t>-14,14; 129,25</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 2,97</t>
+          <t>-3,8; 2,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 7,24</t>
+          <t>-0,71; 7,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 2,12</t>
+          <t>-5,53; 1,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 1,69</t>
+          <t>-8,4; 1,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,38; 77,47</t>
+          <t>-50,99; 68,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 161,71</t>
+          <t>-10,25; 161,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-55,99; 30,18</t>
+          <t>-51,54; 29,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-69,44; 28,56</t>
+          <t>-67,42; 29,29</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 5,19</t>
+          <t>-4,77; 4,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 4,2</t>
+          <t>-9,18; 3,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 6,66</t>
+          <t>-3,59; 5,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 9,11</t>
+          <t>0,09; 8,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-52,97; 108,58</t>
+          <t>-54,08; 95,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-55,86; 47,17</t>
+          <t>-55,43; 38,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-38,84; 170,79</t>
+          <t>-43,22; 141,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 186,73</t>
+          <t>0,23; 169,71</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 4,01</t>
+          <t>-4,7; 3,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 0,72</t>
+          <t>-10,32; 1,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 7,37</t>
+          <t>-2,18; 6,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 3,02</t>
+          <t>-4,96; 3,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-54,06; 98,59</t>
+          <t>-56,25; 100,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,67; 6,71</t>
+          <t>-56,67; 10,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,15; 168,85</t>
+          <t>-27,87; 147,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,69; 55,43</t>
+          <t>-46,11; 48,76</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 1,25</t>
+          <t>-4,44; 1,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 0,71</t>
+          <t>-5,72; 0,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 2,55</t>
+          <t>-3,69; 2,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 0,5</t>
+          <t>-9,15; 0,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-48,06; 23,1</t>
+          <t>-46,68; 25,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-50,78; 12,22</t>
+          <t>-55,06; 5,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-37,45; 41,18</t>
+          <t>-37,95; 38,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-68,67; 4,02</t>
+          <t>-68,84; 8,09</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 3,44</t>
+          <t>-2,3; 3,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,61</t>
+          <t>-1,22; 3,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,06; 5,86</t>
+          <t>-0,06; 5,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 5,16</t>
+          <t>-0,11; 5,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 52,85</t>
+          <t>-24,61; 49,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,41; 92,54</t>
+          <t>-19,56; 97,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 99,54</t>
+          <t>-2,26; 91,1</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 232,8</t>
+          <t>-3,65; 252,57</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 0,73</t>
+          <t>-1,73; 0,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,27</t>
+          <t>-2,67; 0,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,97</t>
+          <t>-0,7; 1,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 2,22</t>
+          <t>-1,03; 2,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-23,42; 11,55</t>
+          <t>-23,63; 10,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 3,53</t>
+          <t>-25,74; 4,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 28,1</t>
+          <t>-8,72; 28,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 40,2</t>
+          <t>-13,69; 43,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A01-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A01-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,39</t>
+          <t>-0,87</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-16,78%</t>
+          <t>-11,7%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 4,81</t>
+          <t>-4,58; 5,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 5,0</t>
+          <t>-6,95; 4,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 2,86</t>
+          <t>-7,04; 2,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 2,56</t>
+          <t>-4,77; 2,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-48,35; 103,61</t>
+          <t>-49,99; 110,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,24; 51,81</t>
+          <t>-43,77; 47,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-53,4; 34,56</t>
+          <t>-51,47; 34,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-53,04; 45,14</t>
+          <t>-47,31; 51,77</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>2,83</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>79,39%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 2,81</t>
+          <t>-3,15; 3,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,42; -0,7</t>
+          <t>-8,69; -0,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 3,51</t>
+          <t>-3,0; 3,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 5,91</t>
+          <t>0,07; 5,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,95; 57,6</t>
+          <t>-40,39; 66,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,7; -5,8</t>
+          <t>-56,38; -6,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,25; 61,71</t>
+          <t>-32,56; 63,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 262,09</t>
+          <t>-2,76; 254,36</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,48</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 0,09</t>
+          <t>-5,31; 0,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 4,35</t>
+          <t>-4,88; 4,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 6,03</t>
+          <t>-2,32; 5,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 6,23</t>
+          <t>-1,88; 5,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-83,21; 17,83</t>
+          <t>-83,84; 16,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,78; 51,01</t>
+          <t>-36,42; 59,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 142,73</t>
+          <t>-31,99; 134,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 129,25</t>
+          <t>-22,18; 100,9</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,59</t>
+          <t>-0,94</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-30,97%</t>
+          <t>-11,6%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 2,92</t>
+          <t>-3,68; 2,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 7,41</t>
+          <t>-0,52; 7,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 1,81</t>
+          <t>-6,09; 1,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,4; 1,69</t>
+          <t>-6,45; 3,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,99; 68,4</t>
+          <t>-51,22; 62,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 161,45</t>
+          <t>-8,77; 166,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-51,54; 29,08</t>
+          <t>-53,76; 26,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,42; 29,29</t>
+          <t>-53,77; 67,74</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,27</t>
+          <t>4,15</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 4,63</t>
+          <t>-4,56; 5,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 3,47</t>
+          <t>-8,69; 3,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 5,92</t>
+          <t>-3,3; 5,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 8,6</t>
+          <t>-0,18; 8,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-54,08; 95,48</t>
+          <t>-51,23; 110,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-55,43; 38,79</t>
+          <t>-55,78; 46,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-43,22; 141,1</t>
+          <t>-37,46; 135,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 169,71</t>
+          <t>-2,81; 164,27</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,94</t>
+          <t>-0,64</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-11,47%</t>
+          <t>-7,9%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 3,88</t>
+          <t>-4,47; 3,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 1,22</t>
+          <t>-10,14; 1,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 6,83</t>
+          <t>-2,85; 6,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 3,0</t>
+          <t>-4,67; 2,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,25; 100,83</t>
+          <t>-57,04; 88,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,67; 10,73</t>
+          <t>-56,6; 12,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,87; 147,24</t>
+          <t>-32,49; 142,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-46,11; 48,76</t>
+          <t>-45,14; 47,86</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-3,17</t>
+          <t>-0,98</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-30,11%</t>
+          <t>-9,14%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 1,68</t>
+          <t>-4,89; 1,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 0,38</t>
+          <t>-5,39; 0,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 2,37</t>
+          <t>-3,77; 2,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 0,83</t>
+          <t>-4,68; 2,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-46,68; 25,14</t>
+          <t>-51,77; 18,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-55,06; 5,37</t>
+          <t>-53,19; 5,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-37,95; 38,94</t>
+          <t>-36,8; 39,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-68,84; 8,09</t>
+          <t>-35,12; 26,88</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 3,36</t>
+          <t>-2,06; 3,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,55</t>
+          <t>-1,19; 3,61</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 5,47</t>
+          <t>-0,05; 6,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 5,21</t>
+          <t>-1,91; 2,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,61; 49,03</t>
+          <t>-21,44; 56,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,56; 97,89</t>
+          <t>-19,36; 93,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 91,1</t>
+          <t>-1,58; 100,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 252,57</t>
+          <t>-29,31; 60,08</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,7</t>
+          <t>-1,73; 0,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,33</t>
+          <t>-2,57; 0,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,98</t>
+          <t>-0,78; 1,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 2,37</t>
+          <t>-0,74; 1,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 10,64</t>
+          <t>-22,35; 11,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-25,74; 4,07</t>
+          <t>-25,06; 3,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 28,16</t>
+          <t>-8,98; 28,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,69; 43,19</t>
+          <t>-9,44; 29,68</t>
         </is>
       </c>
     </row>
